--- a/BOBSAT-1/Physical architecture.xlsx
+++ b/BOBSAT-1/Physical architecture.xlsx
@@ -1,25 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c778b4911c4cd68e/Documents/GitHub/AIAA-Systems-Engineering-Workshop/BOBSAT-1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_F25DC773A252ABDACC104897411C64EE5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DC57655-4E5F-46E0-BABF-B73A4D09B60D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-50" yWindow="0" windowWidth="10830" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Subsystem</t>
+  </si>
+  <si>
+    <t>BOBSAT-1</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>ADCS</t>
+  </si>
+  <si>
+    <t>S&amp;E</t>
+  </si>
+  <si>
+    <t>Payload</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>C&amp;DH</t>
+  </si>
+  <si>
+    <t>elements</t>
+  </si>
+  <si>
+    <t>Solar array</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>wiring</t>
+  </si>
+  <si>
+    <t>Sun sensor</t>
+  </si>
+  <si>
+    <t>Sensors</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Star tracker</t>
+  </si>
+  <si>
+    <t>Magnotometer</t>
+  </si>
+  <si>
+    <t>Gyroscope</t>
+  </si>
+  <si>
+    <t>Actuators</t>
+  </si>
+  <si>
+    <t>Magno torquers</t>
+  </si>
+  <si>
+    <t>Reaction wheels</t>
+  </si>
+  <si>
+    <t>Structural integrity</t>
+  </si>
+  <si>
+    <t>Chassis</t>
+  </si>
+  <si>
+    <t>Thermal management</t>
+  </si>
+  <si>
+    <t>Multi layer insulaiton</t>
+  </si>
+  <si>
+    <t>heat radiators</t>
+  </si>
+  <si>
+    <t>heaters</t>
+  </si>
+  <si>
+    <t>radiation shielding</t>
+  </si>
+  <si>
+    <t>hyperspecral imager</t>
+  </si>
+  <si>
+    <t>hyperscape x50</t>
+  </si>
+  <si>
+    <t>Communications</t>
+  </si>
+  <si>
+    <t>Uplink and downlink antenna</t>
+  </si>
+  <si>
+    <t>Onboard Computer</t>
+  </si>
+  <si>
+    <t>Radio</t>
+  </si>
+  <si>
+    <t>buss assembly</t>
+  </si>
+  <si>
+    <t>Ground computer</t>
+  </si>
+  <si>
+    <t>ground antennas</t>
+  </si>
+  <si>
+    <t>Power generation</t>
+  </si>
+  <si>
+    <t>Power distribution</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +472,211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" customWidth="1"/>
+    <col min="4" max="4" width="27.26953125" customWidth="1"/>
+    <col min="5" max="5" width="25.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>